--- a/Jelovnik.xlsx
+++ b/Jelovnik.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marko\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Jelovnik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DCD5730-2827-4B31-9C05-D459A888F3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFFDC62-39DF-4C90-BDA3-B64DEFB62170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-8310" windowWidth="29040" windowHeight="16440" xr2:uid="{125B7174-242E-4BA1-BBEF-B809F020C994}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="38">
   <si>
     <t>&lt;!DOCTYPE html&gt;
 &lt;html lang="sr"&gt;
@@ -84,9 +84,6 @@
     <t xml:space="preserve">&lt;p class="meal"&gt;Doručak: </t>
   </si>
   <si>
-    <t>Omlet sa povrćem</t>
-  </si>
-  <si>
     <t>&lt;/p&gt;</t>
   </si>
   <si>
@@ -94,12 +91,6 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;p class="meal"&gt;Večera: </t>
-  </si>
-  <si>
-    <t>Pileći file sa pirinčem</t>
-  </si>
-  <si>
-    <t>Supa od paradajza</t>
   </si>
   <si>
     <t xml:space="preserve">          &lt;/div&gt;
@@ -201,6 +192,60 @@
   </si>
   <si>
     <t>Nedelja</t>
+  </si>
+  <si>
+    <t>Vege musaka</t>
+  </si>
+  <si>
+    <t>Špagete bolonjeze</t>
+  </si>
+  <si>
+    <t>Čorba Francias s pirinčem</t>
+  </si>
+  <si>
+    <t>Pastrmka sa prilogom</t>
+  </si>
+  <si>
+    <t>Pita sa bobicama</t>
+  </si>
+  <si>
+    <t>Mafini sa jabukom i šargarepom</t>
+  </si>
+  <si>
+    <t>Pica iz rerne</t>
+  </si>
+  <si>
+    <t>Avokado tost</t>
+  </si>
+  <si>
+    <t>Pita sa sirom</t>
+  </si>
+  <si>
+    <t>Palačinke</t>
+  </si>
+  <si>
+    <t>Prženice</t>
+  </si>
+  <si>
+    <t>Brokoli salata sa tunom</t>
+  </si>
+  <si>
+    <t>Potaž kesten</t>
+  </si>
+  <si>
+    <t>Dimljeni šaran sa batatom</t>
+  </si>
+  <si>
+    <t>Falafeli sa salatom i tahini sosom</t>
+  </si>
+  <si>
+    <t>Kupus salata sa krompirom</t>
+  </si>
+  <si>
+    <t>Zapečene leblebije</t>
+  </si>
+  <si>
+    <t>Grčka meze večera</t>
   </si>
   <si>
     <t>&lt;!DOCTYPE html&gt;
@@ -245,49 +290,49 @@
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="1"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Ponedeljak&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Avokado tost&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Vege musaka&lt;/p&gt;&lt;p class="meal"&gt;Večera: Brokoli salata sa tunom&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Utorak --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="2"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Utorak&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Pita sa bobicama&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Špagete bolonjeze&lt;/p&gt;&lt;p class="meal"&gt;Večera: Potaž kesten&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Sreda --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="3"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Sreda&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Pica iz rerne&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Čorba Francias s pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Falafeli sa salatom i tahini sosom&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Cetvrtak --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="4"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Četvrtak&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Mafini sa jabukom i šargarepom&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Vege musaka&lt;/p&gt;&lt;p class="meal"&gt;Večera: Dimljeni šaran sa batatom&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Petak --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="5"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Petak&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Pita sa sirom&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Špagete bolonjeze&lt;/p&gt;&lt;p class="meal"&gt;Večera: Kupus salata sa krompirom&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Subota --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="6"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Subota&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Palačinke&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Čorba Francias s pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Zapečene leblebije&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Nedelja --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="0"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Nedelja&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Prženice&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pastrmka sa prilogom&lt;/p&gt;&lt;p class="meal"&gt;Večera: Grčka meze večera&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
     &lt;/div&gt;
@@ -682,375 +727,375 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" t="str">
         <f>_xlfn.CONCAT(C2:E2)</f>
-        <v>&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Doručak: Avokado tost&lt;/p&gt;</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" t="str">
         <f t="shared" ref="B3:B4" si="0">_xlfn.CONCAT(C3:E3)</f>
-        <v>&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Ručak: Vege musaka&lt;/p&gt;</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Večera: Brokoli salata sa tunom&lt;/p&gt;</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" t="str">
         <f>_xlfn.CONCAT(C6:E6)</f>
-        <v>&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Doručak: Pita sa bobicama&lt;/p&gt;</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" t="str">
         <f t="shared" ref="B7:B8" si="1">_xlfn.CONCAT(C7:E7)</f>
-        <v>&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Ručak: Špagete bolonjeze&lt;/p&gt;</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" t="str">
         <f t="shared" si="1"/>
-        <v>&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Večera: Potaž kesten&lt;/p&gt;</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" t="str">
         <f>_xlfn.CONCAT(C10:E10)</f>
-        <v>&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Doručak: Pica iz rerne&lt;/p&gt;</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" t="str">
         <f t="shared" ref="B11:B12" si="2">_xlfn.CONCAT(C11:E11)</f>
-        <v>&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Ručak: Čorba Francias s pirinčem&lt;/p&gt;</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Večera: Falafeli sa salatom i tahini sosom&lt;/p&gt;</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" t="str">
         <f>_xlfn.CONCAT(C14:E14)</f>
-        <v>&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Doručak: Mafini sa jabukom i šargarepom&lt;/p&gt;</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" t="str">
         <f t="shared" ref="B15:B16" si="3">_xlfn.CONCAT(C15:E15)</f>
-        <v>&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Ručak: Vege musaka&lt;/p&gt;</v>
       </c>
       <c r="C15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Večera: Dimljeni šaran sa batatom&lt;/p&gt;</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" t="str">
         <f>_xlfn.CONCAT(C18:E18)</f>
-        <v>&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Doručak: Pita sa sirom&lt;/p&gt;</v>
       </c>
       <c r="C18" t="s">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" t="str">
         <f t="shared" ref="B19:B20" si="4">_xlfn.CONCAT(C19:E19)</f>
-        <v>&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Ručak: Špagete bolonjeze&lt;/p&gt;</v>
       </c>
       <c r="C19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" t="str">
         <f t="shared" si="4"/>
-        <v>&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Večera: Kupus salata sa krompirom&lt;/p&gt;</v>
       </c>
       <c r="C20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" t="str">
         <f>_xlfn.CONCAT(C22:E22)</f>
-        <v>&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Doručak: Palačinke&lt;/p&gt;</v>
       </c>
       <c r="C22" t="s">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" t="str">
         <f t="shared" ref="B23:B24" si="5">_xlfn.CONCAT(C23:E23)</f>
-        <v>&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Ručak: Čorba Francias s pirinčem&lt;/p&gt;</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" t="str">
         <f t="shared" si="5"/>
-        <v>&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Večera: Zapečene leblebije&lt;/p&gt;</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" t="str">
         <f>_xlfn.CONCAT(C26:E26)</f>
-        <v>&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Doručak: Prženice&lt;/p&gt;</v>
       </c>
       <c r="C26" t="s">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" t="str">
         <f t="shared" ref="B27:B28" si="6">_xlfn.CONCAT(C27:E27)</f>
-        <v>&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Ručak: Pastrmka sa prilogom&lt;/p&gt;</v>
       </c>
       <c r="C27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" t="str">
         <f t="shared" si="6"/>
-        <v>&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;</v>
+        <v>&lt;p class="meal"&gt;Večera: Grčka meze večera&lt;/p&gt;</v>
       </c>
       <c r="C28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.35">
@@ -1099,49 +1144,49 @@
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="1"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Ponedeljak&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Avokado tost&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Vege musaka&lt;/p&gt;&lt;p class="meal"&gt;Večera: Brokoli salata sa tunom&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Utorak --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="2"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Utorak&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Pita sa bobicama&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Špagete bolonjeze&lt;/p&gt;&lt;p class="meal"&gt;Večera: Potaž kesten&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Sreda --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="3"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Sreda&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Pica iz rerne&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Čorba Francias s pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Falafeli sa salatom i tahini sosom&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Cetvrtak --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="4"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Četvrtak&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Mafini sa jabukom i šargarepom&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Vege musaka&lt;/p&gt;&lt;p class="meal"&gt;Večera: Dimljeni šaran sa batatom&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Petak --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="5"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Petak&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Pita sa sirom&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Špagete bolonjeze&lt;/p&gt;&lt;p class="meal"&gt;Večera: Kupus salata sa krompirom&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Subota --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="6"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Subota&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Palačinke&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Čorba Francias s pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Zapečene leblebije&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
       &lt;!-- Nedelja --&gt;
       &lt;div class="col"&gt;
         &lt;div class="card day-card" data-day="0"&gt;
           &lt;div class="card-header bg-success text-white"&gt;Nedelja&lt;/div&gt;
-          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Omlet sa povrćem&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pileći file sa pirinčem&lt;/p&gt;&lt;p class="meal"&gt;Večera: Supa od paradajza&lt;/p&gt;          &lt;/div&gt;
+          &lt;div class="card-body"&gt;&lt;p class="meal"&gt;Doručak: Prženice&lt;/p&gt;&lt;p class="meal"&gt;Ručak: Pastrmka sa prilogom&lt;/p&gt;&lt;p class="meal"&gt;Večera: Grčka meze večera&lt;/p&gt;          &lt;/div&gt;
         &lt;/div&gt;
       &lt;/div&gt;
     &lt;/div&gt;
@@ -1161,9 +1206,9 @@
 &lt;/html&gt;</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="D31" t="s">
-        <v>22</v>
+    <row r="31" spans="2:5" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="D31" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
